--- a/inputs/portfolio.xlsx
+++ b/inputs/portfolio.xlsx
@@ -55,10 +55,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -433,6 +436,8 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,6 +466,16 @@
           <t>Website</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Key competitors</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>What moves them</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,7 +498,16 @@
           <t>India</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>sugar.fit, Twin Health, Fitterfly, Wellthy Therapeutics</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Rising Indian diabetes/pre-diabetes prevalence and cheaper CGMs expand the market; wide GLP-1 adoption (Mounjaro/Wegovy now in India) is both a tailwind (new paid weight/metabolic programs) and a risk if pharma or pure-play weight-loss players capture that revenue directly.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,7 +530,16 @@
           <t>India</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FirstCry, BabyChakra (Mosaic Wellness), The Moms Co, Mamaearth</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Sensitive to D2C economics — digital ad costs, quick-commerce/marketplace shelf competition from FirstCry and Mamaearth, and the funding climate; India's urban birth rate and young-parent spending set the ceiling on the base.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -529,7 +562,16 @@
           <t>India</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Bold Care, Man Matters (Mosaic Wellness), Kindly Health, Allo Health</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tightening regulation on tele-prescribing of sexual-health and weight-loss drugs (and ad-platform limits on the category) is the main risk; the 2023 Mojocare fraud collapse dented sector trust/funding, while GLP-1 availability opens a new prescription weight-loss line.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -552,7 +594,16 @@
           <t>India</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>sugar.fit, HealthifyMe, Fitterfly, BeatO (weight line)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>The 2025 India launches of branded GLP-1s (Lilly Mounjaro, Novo Wegovy) are a direct demand tailwind, but drug pricing, supply/shortages, regulatory limits on GLP-1 prescribing for weight loss, and pharma/pharmacies going direct-to-consumer are the biggest swings.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -575,7 +626,16 @@
           <t>India</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Rainbow Children's Medicare, Cloudnine, Babynama</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Urban private-pay demand, so disposable-income swings and any shift in OPD/pediatric insurance coverage matter; national immunization-schedule changes and hospital chains adding pediatric outpatient wings pressure core vaccination + primary-care volume.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -598,7 +658,16 @@
           <t>India</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>QI Spine Clinic; broadly hospital orthopedic/spine departments and physiotherapy chains (few pure-play interventional-pain chains — largely category-defining)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Insurance/reimbursement recognition of interventional pain procedures as covered daycare treatment is the biggest lever; an aging population and rising chronic back/knee pain expand demand, while surgeons steering patients to surgery and unregulated clinics compete for the same patients.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -621,7 +690,16 @@
           <t>India</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>n/a (positions as India's first healthcare venture studio; closest analog is Redesign Health in the US)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>The health-tech funding climate and exit/IPO environment drive both its capital (W Health fund cycles / LP appetite) and its ability to spin out fundable companies; strong portfolio outcomes validate the model, a funding winter or a portfolio flop undercuts it.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -644,7 +722,16 @@
           <t>India</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>HealthCare Global (HCG), Cytecare, American Oncology Institute; troubled peer Karkinos Healthcare</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Insurance/reimbursement coverage for outpatient daycare chemotherapy and cancer-drug pricing/access are decisive for its transparency/EMI model; rising cancer incidence and its Narayana Health clinical partnership are tailwinds, while hospital oncology departments and regulatory tightening on standalone daycare oncology are risks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -667,7 +754,16 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>n/a (early/stealth)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Cannot be assessed without a defined product; broadly, India–US trade/tariff policy, IT/services outsourcing demand, and US visa/immigration rules would plausibly affect a cross-border B2B services play. *(Keyword news-matching won't work until a name/product is public.)*</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -690,7 +786,16 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Woebot, Headspace, Spring Health, Lyra Health, Ieso/Limbic</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>FDA/NHS/regulatory posture on AI-driven mental-health tools and payer reimbursement for digital therapeutics drive adoption; safety scrutiny of AI chatbots and employer-benefit budget cycles are the main downside risks. **Linked to Kins (owns it) — news on one is relevant to the other.**</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -713,7 +818,16 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Thyme Care, Reimagine Care, AccessHope, OncoHealth</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>CMS reimbursement for cancer navigation / principal illness navigation and Health-Related Social Needs codes directly expand or contract its payer market; oncology drug/cost trends and health-plan value-based-care appetite also move demand.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -736,7 +850,16 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Luna, Hinge Health, Sword Health, IncludeHealth</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Medicare/commercial PT reimbursement rates and telehealth-coverage rules drive unit economics; MSK point-solution consolidation (and its own integration into Wysa) plus employer/payer MSK spend shape the trajectory.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -759,7 +882,16 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Quality Interactions, Included Health (equity/navigation); largely niche otherwise</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Demand is tied to DEI/health-equity spending and mandates (NCQA health-equity accreditation, CMS equity measures) — a policy/political retreat from DEI or equity reporting shrinks buyer budgets; renewed equity mandates expand them.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -782,7 +914,16 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>CitiusTech, ThoughtWorks, Persistent Systems; boutique healthcare-AI shops</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Rides enterprise healthcare AI/gen-AI adoption budgets — HIPAA/FDA rules on clinical AI, hospital IT spend cycles, and the build-vs-buy shift toward in-house AI drive demand; a pullback in healthcare AI spend or commoditization by hyperscaler/LLM tooling erodes it.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -805,7 +946,16 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Virta Health, Omada Health, Vida Health, Cecelia Health</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Payer appetite for value-based/risk contracts and CGM reimbursement coverage; GLP-1 drug economics cut both ways (raising diabetes-management urgency but offering a competing pharma-only fix); Medicaid/commercial coverage shifts affect the addressable population.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -828,7 +978,16 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Osmind, Greenbrook TMS, Salience Health / Mindful Health Solutions</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Highly sensitive to payer reimbursement and prior-auth policy for TMS and SPRAVATO and to FDA label expansions; expanded coverage/indications grow the pipeline, reimbursement cuts or tighter prior-auth criteria threaten the economics it exists to unlock.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
